--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-Next-80B-A3B-Instruct/aae/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-2-7b-chat-hf/Qwen3-Next-80B-A3B-Instruct/aae/total_votes_file.xlsx
@@ -430,10 +430,10 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="D2">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="D3">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>426</v>
